--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="316">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -981,6 +981,10 @@
   </si>
   <si>
     <t>The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>not supported</t>
@@ -5469,10 +5473,10 @@
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -5480,10 +5484,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5509,14 +5513,14 @@
         <v>305</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -5565,22 +5569,22 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AK39" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="376">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -619,13 +619,208 @@
     <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
+    <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>.routeCode</t>
+  </si>
+  <si>
+    <t>RXR-1</t>
+  </si>
+  <si>
+    <t>Dosage.route.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.extension</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
     <t>https://termgit.elga.gv.at/CodeSystem/medikationartanwendung</t>
   </si>
   <si>
-    <t>.routeCode</t>
-  </si>
-  <si>
-    <t>RXR-1</t>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Dosage.route.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -677,16 +872,6 @@
     <t>Dosage.doseAndRate.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.type</t>
   </si>
   <si>
@@ -803,10 +988,6 @@
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x].comparator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
   </si>
   <si>
     <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
@@ -1320,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL39"/>
+  <dimension ref="A1:AL50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.88671875" customWidth="true" bestFit="true"/>
@@ -1359,7 +1540,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="109.8359375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3481,11 +3662,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3518,18 +3701,18 @@
         <v>79</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3543,29 +3726,25 @@
         <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>84</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -3589,13 +3768,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>201</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -3613,7 +3792,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>86</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3625,52 +3804,54 @@
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3707,19 +3888,19 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>95</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3731,21 +3912,21 @@
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3756,7 +3937,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3765,19 +3946,23 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -3825,25 +4010,25 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>87</v>
+        <v>209</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -3855,14 +4040,14 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3874,17 +4059,15 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -3921,31 +4104,31 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>87</v>
@@ -3956,21 +4139,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3979,21 +4162,21 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4017,57 +4200,57 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>221</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4090,19 +4273,19 @@
         <v>126</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>223</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4112,7 +4295,7 @@
         <v>20</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>20</v>
@@ -4139,17 +4322,19 @@
         <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4164,22 +4349,20 @@
         <v>79</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="C27" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>20</v>
       </c>
@@ -4191,7 +4374,7 @@
         <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
@@ -4200,20 +4383,18 @@
         <v>126</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M27" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>227</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -4261,7 +4442,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4276,22 +4457,20 @@
         <v>79</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>228</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4303,7 +4482,7 @@
         <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
@@ -4312,19 +4491,17 @@
         <v>126</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4373,7 +4550,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4388,10 +4565,10 @@
         <v>79</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -4399,7 +4576,7 @@
         <v>237</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4419,19 +4596,21 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>84</v>
+        <v>238</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>85</v>
+        <v>239</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -4479,7 +4658,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>86</v>
+        <v>241</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4491,32 +4670,32 @@
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>87</v>
+        <v>242</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4525,21 +4704,23 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -4575,45 +4756,45 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>95</v>
+        <v>249</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>87</v>
+        <v>250</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4636,19 +4817,19 @@
         <v>126</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -4697,7 +4878,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4712,18 +4893,18 @@
         <v>79</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4734,36 +4915,36 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>126</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>253</v>
+        <v>116</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q32" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
         <v>20</v>
       </c>
@@ -4783,13 +4964,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -4822,18 +5003,18 @@
         <v>79</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4847,7 +5028,7 @@
         <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
@@ -4856,18 +5037,16 @@
         <v>126</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>83</v>
+        <v>270</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -4891,11 +5070,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -4919,7 +5100,7 @@
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -4928,18 +5109,18 @@
         <v>79</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4959,21 +5140,19 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>85</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>276</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5021,7 +5200,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>277</v>
+        <v>86</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5030,35 +5209,35 @@
         <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>278</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>87</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5067,23 +5246,21 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>253</v>
+        <v>89</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>200</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>201</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5119,45 +5296,45 @@
         <v>20</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>95</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>287</v>
+        <v>87</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5180,19 +5357,17 @@
         <v>126</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5217,13 +5392,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>281</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5241,7 +5416,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5256,18 +5431,18 @@
         <v>79</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>294</v>
+        <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>295</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5290,19 +5465,19 @@
         <v>126</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5339,19 +5514,17 @@
         <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5366,20 +5539,22 @@
         <v>79</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="38" hidden="true">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>20</v>
       </c>
@@ -5391,7 +5566,7 @@
         <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
@@ -5400,19 +5575,19 @@
         <v>126</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -5461,7 +5636,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5473,23 +5648,25 @@
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>311</v>
+        <v>267</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" hidden="true">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
       </c>
@@ -5501,7 +5678,7 @@
         <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -5510,17 +5687,19 @@
         <v>126</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -5569,29 +5748,1225 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AL39" t="s" s="2">
+      <c r="B43" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q43" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="R43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y44" s="2"/>
+      <c r="Z44" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL39">
+  <autoFilter ref="A1:AL50">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5601,7 +6976,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI38">
+  <conditionalFormatting sqref="A2:AI49">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1358,7 +1358,7 @@
     <t>TODO</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationmengenart</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x]:doseQuantity.id</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -674,7 +674,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>Freitext-Dosierungsanweisung, wenn keine strukturierte Angabe möglich ist.</t>
+    <t>Textdarstellung der Dosierung: bei strukturierter Dosierung durch die Fachanwendung generiert, sonst Freitext-Dosierungsanweisung (wenn keine strukturierte Angabe möglich ist).</t>
   </si>
   <si>
     <t>Free text dosage instructions e.g. SIG.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -294,6 +294,9 @@
     <t>Dosage.extension</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
@@ -325,9 +328,6 @@
   </si>
   <si>
     <t>DosageCategory</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category}
@@ -2560,7 +2560,7 @@
         <v>77</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -2569,13 +2569,13 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2614,19 +2614,19 @@
         <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
@@ -2638,7 +2638,7 @@
         <v>21</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>21</v>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>21</v>
@@ -2668,7 +2668,7 @@
         <v>77</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>21</v>
@@ -2734,7 +2734,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2746,7 +2746,7 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -2889,13 +2889,13 @@
         <v>21</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2934,19 +2934,19 @@
         <v>21</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2958,7 +2958,7 @@
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>21</v>
@@ -2986,7 +2986,7 @@
         <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
@@ -3094,7 +3094,7 @@
         <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>21</v>
@@ -3315,7 +3315,7 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>131</v>
@@ -3362,19 +3362,19 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3386,7 +3386,7 @@
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>89</v>
@@ -3414,13 +3414,13 @@
         <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
         <v>136</v>
@@ -3639,7 +3639,7 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>131</v>
@@ -3686,19 +3686,19 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3710,7 +3710,7 @@
         <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>89</v>
@@ -3738,13 +3738,13 @@
         <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>110</v>
@@ -3848,13 +3848,13 @@
         <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>85</v>
@@ -3956,13 +3956,13 @@
         <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>168</v>
@@ -4064,13 +4064,13 @@
         <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>85</v>
@@ -4178,7 +4178,7 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>186</v>
@@ -4288,7 +4288,7 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>85</v>
@@ -4395,19 +4395,19 @@
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>204</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4470,7 +4470,7 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
@@ -4498,13 +4498,13 @@
         <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>207</v>
@@ -4606,13 +4606,13 @@
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>85</v>
@@ -4714,13 +4714,13 @@
         <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>119</v>
@@ -4939,7 +4939,7 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>131</v>
@@ -4986,19 +4986,19 @@
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5010,7 +5010,7 @@
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>89</v>
@@ -5038,13 +5038,13 @@
         <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>136</v>
@@ -5263,7 +5263,7 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>131</v>
@@ -5310,19 +5310,19 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5334,7 +5334,7 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>89</v>
@@ -5362,13 +5362,13 @@
         <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>110</v>
@@ -5472,13 +5472,13 @@
         <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>85</v>
@@ -5580,13 +5580,13 @@
         <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>168</v>
@@ -5688,13 +5688,13 @@
         <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>85</v>
@@ -5802,7 +5802,7 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>186</v>
@@ -5912,7 +5912,7 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>85</v>
@@ -6016,13 +6016,13 @@
         <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>85</v>
@@ -6122,13 +6122,13 @@
         <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>242</v>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>186</v>
@@ -6340,13 +6340,13 @@
         <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>119</v>
@@ -6565,7 +6565,7 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>131</v>
@@ -6612,19 +6612,19 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6636,7 +6636,7 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>89</v>
@@ -6664,13 +6664,13 @@
         <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>136</v>
@@ -6889,7 +6889,7 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>131</v>
@@ -6936,19 +6936,19 @@
         <v>21</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6960,7 +6960,7 @@
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>89</v>
@@ -6988,13 +6988,13 @@
         <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>110</v>
@@ -7098,13 +7098,13 @@
         <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>85</v>
@@ -7206,13 +7206,13 @@
         <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>168</v>
@@ -7314,13 +7314,13 @@
         <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>85</v>
@@ -7428,7 +7428,7 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>186</v>
@@ -7538,7 +7538,7 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>85</v>
@@ -7642,13 +7642,13 @@
         <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>119</v>
@@ -7865,7 +7865,7 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>131</v>
@@ -7912,19 +7912,19 @@
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7936,7 +7936,7 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>89</v>
@@ -7964,13 +7964,13 @@
         <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>136</v>
@@ -8189,7 +8189,7 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>131</v>
@@ -8236,19 +8236,19 @@
         <v>21</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8260,7 +8260,7 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>89</v>
@@ -8288,13 +8288,13 @@
         <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>110</v>
@@ -8398,13 +8398,13 @@
         <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>85</v>
@@ -8506,13 +8506,13 @@
         <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>168</v>
@@ -8614,13 +8614,13 @@
         <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>85</v>
@@ -8728,7 +8728,7 @@
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>186</v>
@@ -8838,7 +8838,7 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>85</v>
@@ -8942,13 +8942,13 @@
         <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>119</v>
@@ -9167,7 +9167,7 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>131</v>
@@ -9214,19 +9214,19 @@
         <v>21</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9238,7 +9238,7 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>89</v>
@@ -9266,13 +9266,13 @@
         <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>136</v>
@@ -9491,7 +9491,7 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>131</v>
@@ -9538,19 +9538,19 @@
         <v>21</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9562,7 +9562,7 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>89</v>
@@ -9590,13 +9590,13 @@
         <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>110</v>
@@ -9700,13 +9700,13 @@
         <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>85</v>
@@ -9808,13 +9808,13 @@
         <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>168</v>
@@ -9916,13 +9916,13 @@
         <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>85</v>
@@ -10030,7 +10030,7 @@
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>186</v>
@@ -10140,7 +10140,7 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>85</v>
@@ -10244,13 +10244,13 @@
         <v>84</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>315</v>
@@ -10465,7 +10465,7 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>131</v>
@@ -10512,19 +10512,19 @@
         <v>21</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10536,7 +10536,7 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>89</v>
@@ -10570,7 +10570,7 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>119</v>
@@ -10672,13 +10672,13 @@
         <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>329</v>
@@ -10782,13 +10782,13 @@
         <v>84</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>339</v>
@@ -11007,7 +11007,7 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>131</v>
@@ -11054,19 +11054,19 @@
         <v>21</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11078,7 +11078,7 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>89</v>
@@ -11106,13 +11106,13 @@
         <v>84</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>347</v>
@@ -11329,7 +11329,7 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>131</v>
@@ -11376,19 +11376,19 @@
         <v>21</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11400,7 +11400,7 @@
         <v>21</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>89</v>
@@ -11428,13 +11428,13 @@
         <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>361</v>
@@ -11541,10 +11541,10 @@
         <v>21</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>168</v>
@@ -11648,13 +11648,13 @@
         <v>84</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>85</v>
@@ -11756,13 +11756,13 @@
         <v>84</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>110</v>
@@ -11864,13 +11864,13 @@
         <v>84</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>168</v>
@@ -11974,13 +11974,13 @@
         <v>84</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>347</v>
@@ -12197,7 +12197,7 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>131</v>
@@ -12244,19 +12244,19 @@
         <v>21</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12268,7 +12268,7 @@
         <v>21</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>89</v>
@@ -12296,13 +12296,13 @@
         <v>84</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>361</v>
@@ -12409,10 +12409,10 @@
         <v>21</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>168</v>
@@ -12516,13 +12516,13 @@
         <v>84</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>85</v>
@@ -12624,13 +12624,13 @@
         <v>84</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>110</v>
@@ -12732,13 +12732,13 @@
         <v>84</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>168</v>
@@ -12844,13 +12844,13 @@
         <v>84</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>428</v>
@@ -13067,7 +13067,7 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>131</v>
@@ -13114,19 +13114,19 @@
         <v>21</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13138,7 +13138,7 @@
         <v>21</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>89</v>
@@ -13166,13 +13166,13 @@
         <v>84</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>361</v>
@@ -13279,10 +13279,10 @@
         <v>21</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
         <v>168</v>
@@ -13386,13 +13386,13 @@
         <v>84</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>85</v>
@@ -13494,13 +13494,13 @@
         <v>84</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>110</v>
@@ -13602,13 +13602,13 @@
         <v>84</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>168</v>
@@ -13712,13 +13712,13 @@
         <v>84</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>444</v>
@@ -13822,13 +13822,13 @@
         <v>84</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>428</v>
@@ -14047,7 +14047,7 @@
         <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>131</v>
@@ -14094,19 +14094,19 @@
         <v>21</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14118,7 +14118,7 @@
         <v>21</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>89</v>
@@ -14146,13 +14146,13 @@
         <v>84</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>361</v>
@@ -14259,10 +14259,10 @@
         <v>21</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>168</v>
@@ -14366,13 +14366,13 @@
         <v>84</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
         <v>85</v>
@@ -14474,13 +14474,13 @@
         <v>84</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
         <v>110</v>
@@ -14582,13 +14582,13 @@
         <v>84</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>168</v>
@@ -14694,13 +14694,13 @@
         <v>84</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>339</v>
@@ -14919,7 +14919,7 @@
         <v>21</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>131</v>
@@ -14966,19 +14966,19 @@
         <v>21</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -14990,7 +14990,7 @@
         <v>21</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>89</v>
@@ -15018,13 +15018,13 @@
         <v>84</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>347</v>
@@ -15241,7 +15241,7 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L121" t="s" s="2">
         <v>131</v>
@@ -15288,19 +15288,19 @@
         <v>21</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15312,7 +15312,7 @@
         <v>21</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>89</v>
@@ -15340,13 +15340,13 @@
         <v>84</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
         <v>361</v>
@@ -15453,10 +15453,10 @@
         <v>21</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
         <v>168</v>
@@ -15560,13 +15560,13 @@
         <v>84</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
         <v>85</v>
@@ -15668,13 +15668,13 @@
         <v>84</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
         <v>110</v>
@@ -15776,13 +15776,13 @@
         <v>84</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>168</v>
@@ -15886,13 +15886,13 @@
         <v>84</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
         <v>347</v>
@@ -16109,7 +16109,7 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>131</v>
@@ -16156,19 +16156,19 @@
         <v>21</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC129" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -16180,7 +16180,7 @@
         <v>21</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>89</v>
@@ -16208,13 +16208,13 @@
         <v>84</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
         <v>361</v>
@@ -16321,10 +16321,10 @@
         <v>21</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>168</v>
@@ -16428,13 +16428,13 @@
         <v>84</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
         <v>85</v>
@@ -16536,13 +16536,13 @@
         <v>84</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
         <v>110</v>
@@ -16644,13 +16644,13 @@
         <v>84</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>168</v>
@@ -16756,13 +16756,13 @@
         <v>84</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
         <v>506</v>
@@ -16981,7 +16981,7 @@
         <v>21</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>131</v>
@@ -17028,19 +17028,19 @@
         <v>21</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -17052,7 +17052,7 @@
         <v>21</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>89</v>
@@ -17080,13 +17080,13 @@
         <v>84</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
         <v>511</v>
@@ -17301,7 +17301,7 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L140" t="s" s="2">
         <v>131</v>
@@ -17348,19 +17348,19 @@
         <v>21</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC140" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -17372,7 +17372,7 @@
         <v>21</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>89</v>
@@ -17400,13 +17400,13 @@
         <v>84</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
         <v>361</v>
@@ -17513,10 +17513,10 @@
         <v>21</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>168</v>
@@ -17620,13 +17620,13 @@
         <v>84</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
         <v>85</v>
@@ -17728,13 +17728,13 @@
         <v>84</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K144" t="s" s="2">
         <v>110</v>
@@ -17836,13 +17836,13 @@
         <v>84</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K145" t="s" s="2">
         <v>168</v>
@@ -17946,13 +17946,13 @@
         <v>84</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>511</v>
@@ -18167,7 +18167,7 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L148" t="s" s="2">
         <v>131</v>
@@ -18214,19 +18214,19 @@
         <v>21</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC148" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD148" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -18238,7 +18238,7 @@
         <v>21</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>89</v>
@@ -18266,13 +18266,13 @@
         <v>84</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
         <v>361</v>
@@ -18379,10 +18379,10 @@
         <v>21</v>
       </c>
       <c r="I150" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
         <v>168</v>
@@ -18486,13 +18486,13 @@
         <v>84</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
         <v>85</v>
@@ -18594,13 +18594,13 @@
         <v>84</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
         <v>110</v>
@@ -18702,13 +18702,13 @@
         <v>84</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K153" t="s" s="2">
         <v>168</v>
@@ -18812,13 +18812,13 @@
         <v>84</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K154" t="s" s="2">
         <v>506</v>
@@ -19037,7 +19037,7 @@
         <v>21</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L156" t="s" s="2">
         <v>131</v>
@@ -19084,19 +19084,19 @@
         <v>21</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -19108,7 +19108,7 @@
         <v>21</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>89</v>
@@ -19136,13 +19136,13 @@
         <v>84</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K157" t="s" s="2">
         <v>511</v>
@@ -19357,7 +19357,7 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>131</v>
@@ -19404,19 +19404,19 @@
         <v>21</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -19428,7 +19428,7 @@
         <v>21</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>89</v>
@@ -19456,13 +19456,13 @@
         <v>84</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
         <v>361</v>
@@ -19569,10 +19569,10 @@
         <v>21</v>
       </c>
       <c r="I161" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K161" t="s" s="2">
         <v>168</v>
@@ -19676,13 +19676,13 @@
         <v>84</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K162" t="s" s="2">
         <v>85</v>
@@ -19784,13 +19784,13 @@
         <v>84</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
         <v>110</v>
@@ -19892,13 +19892,13 @@
         <v>84</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
         <v>168</v>
@@ -20002,13 +20002,13 @@
         <v>84</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K165" t="s" s="2">
         <v>511</v>
@@ -20223,7 +20223,7 @@
         <v>21</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L167" t="s" s="2">
         <v>131</v>
@@ -20270,19 +20270,19 @@
         <v>21</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
@@ -20294,7 +20294,7 @@
         <v>21</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>89</v>
@@ -20322,13 +20322,13 @@
         <v>84</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>361</v>
@@ -20435,10 +20435,10 @@
         <v>21</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>168</v>
@@ -20542,13 +20542,13 @@
         <v>84</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
         <v>85</v>
@@ -20650,13 +20650,13 @@
         <v>84</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
         <v>110</v>
@@ -20758,13 +20758,13 @@
         <v>84</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
         <v>168</v>
@@ -20868,13 +20868,13 @@
         <v>84</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K173" t="s" s="2">
         <v>347</v>
@@ -21093,7 +21093,7 @@
         <v>21</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L175" t="s" s="2">
         <v>131</v>
@@ -21140,19 +21140,19 @@
         <v>21</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -21164,7 +21164,7 @@
         <v>21</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>89</v>
@@ -21192,13 +21192,13 @@
         <v>84</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I176" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K176" t="s" s="2">
         <v>361</v>
@@ -21305,10 +21305,10 @@
         <v>21</v>
       </c>
       <c r="I177" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K177" t="s" s="2">
         <v>168</v>
@@ -21412,13 +21412,13 @@
         <v>84</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K178" t="s" s="2">
         <v>85</v>
@@ -21520,13 +21520,13 @@
         <v>84</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K179" t="s" s="2">
         <v>110</v>
@@ -21628,13 +21628,13 @@
         <v>84</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K180" t="s" s="2">
         <v>168</v>
@@ -21738,13 +21738,13 @@
         <v>84</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K181" t="s" s="2">
         <v>347</v>
@@ -21961,7 +21961,7 @@
         <v>21</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L183" t="s" s="2">
         <v>131</v>
@@ -22008,19 +22008,19 @@
         <v>21</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -22032,7 +22032,7 @@
         <v>21</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>89</v>
@@ -22060,13 +22060,13 @@
         <v>84</v>
       </c>
       <c r="H184" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I184" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K184" t="s" s="2">
         <v>361</v>
@@ -22173,10 +22173,10 @@
         <v>21</v>
       </c>
       <c r="I185" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K185" t="s" s="2">
         <v>168</v>
@@ -22280,13 +22280,13 @@
         <v>84</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
         <v>85</v>
@@ -22388,13 +22388,13 @@
         <v>84</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
         <v>110</v>
@@ -22496,13 +22496,13 @@
         <v>84</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K188" t="s" s="2">
         <v>168</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -399,7 +399,7 @@
     <t>Code für die Art der Dosierung</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetDosageCategory</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-dosagecategory-vs</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -491,7 +491,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/AtElgaEmedCodeSystemDosageCategory</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/at-elga-emed-codesystem-dosagecategory-cs</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -2199,7 +2199,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6466" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6466" uniqueCount="601">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -619,7 +619,7 @@
     <t>Dosage.extension.value[x].text</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>Plain text representation of the concept</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -857,6 +857,9 @@
     <t>Dosage.site.text</t>
   </si>
   <si>
+    <t>Fachliche Begründung: TODO</t>
+  </si>
+  <si>
     <t>Dosage.route</t>
   </si>
   <si>
@@ -1331,7 +1334,7 @@
 </t>
   </si>
   <si>
-    <t>TODO</t>
+    <t>Amount of medication per dose</t>
   </si>
   <si>
     <t>https://termgit.elga.gv.at/ValueSet/elga-medikationmengenart</t>
@@ -7544,7 +7547,7 @@
         <v>85</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>197</v>
@@ -7625,10 +7628,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7654,14 +7657,14 @@
         <v>119</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7689,10 +7692,10 @@
         <v>223</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7710,7 +7713,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7725,18 +7728,18 @@
         <v>81</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7839,10 +7842,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7947,10 +7950,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8057,10 +8060,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8163,10 +8166,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8271,10 +8274,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8319,7 +8322,7 @@
         <v>21</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>21</v>
@@ -8381,10 +8384,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8489,10 +8492,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8597,10 +8600,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8705,10 +8708,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8815,10 +8818,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8844,7 +8847,7 @@
         <v>85</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>197</v>
@@ -8925,10 +8928,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8954,16 +8957,16 @@
         <v>119</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -8991,10 +8994,10 @@
         <v>223</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9012,7 +9015,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9027,18 +9030,18 @@
         <v>81</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9141,10 +9144,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9249,10 +9252,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9359,10 +9362,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9465,10 +9468,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9573,10 +9576,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9683,10 +9686,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9791,10 +9794,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9899,10 +9902,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10007,10 +10010,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10117,10 +10120,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10146,7 +10149,7 @@
         <v>85</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>197</v>
@@ -10227,10 +10230,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10253,13 +10256,13 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10310,7 +10313,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10328,15 +10331,15 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10439,10 +10442,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10547,10 +10550,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10576,14 +10579,14 @@
         <v>119</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10611,10 +10614,10 @@
         <v>223</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -10632,7 +10635,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10650,15 +10653,15 @@
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10681,19 +10684,19 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -10730,17 +10733,17 @@
         <v>21</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AC79" s="2"/>
       <c r="AD79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10755,21 +10758,21 @@
         <v>81</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>21</v>
@@ -10791,19 +10794,19 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -10852,7 +10855,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -10867,18 +10870,18 @@
         <v>81</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10981,10 +10984,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11089,10 +11092,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11115,16 +11118,16 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11174,7 +11177,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11186,21 +11189,21 @@
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11303,10 +11306,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11411,10 +11414,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11437,19 +11440,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -11498,7 +11501,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11513,18 +11516,18 @@
         <v>81</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11550,20 +11553,20 @@
         <v>168</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q87" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R87" t="s" s="2">
         <v>21</v>
@@ -11587,10 +11590,10 @@
         <v>122</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
@@ -11608,7 +11611,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -11623,18 +11626,18 @@
         <v>81</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11660,14 +11663,14 @@
         <v>85</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -11716,7 +11719,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -11731,18 +11734,18 @@
         <v>81</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11768,14 +11771,14 @@
         <v>110</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -11824,7 +11827,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -11833,24 +11836,24 @@
         <v>84</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11876,16 +11879,16 @@
         <v>168</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -11934,7 +11937,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11949,18 +11952,18 @@
         <v>81</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11983,16 +11986,16 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12042,7 +12045,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12054,21 +12057,21 @@
         <v>21</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12171,10 +12174,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12279,10 +12282,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12305,19 +12308,19 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
@@ -12366,7 +12369,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12381,18 +12384,18 @@
         <v>81</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12418,20 +12421,20 @@
         <v>168</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q95" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R95" t="s" s="2">
         <v>21</v>
@@ -12455,10 +12458,10 @@
         <v>122</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>21</v>
@@ -12476,7 +12479,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -12491,18 +12494,18 @@
         <v>81</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12528,14 +12531,14 @@
         <v>85</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -12584,7 +12587,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -12599,18 +12602,18 @@
         <v>81</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12636,14 +12639,14 @@
         <v>110</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -12692,7 +12695,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12701,24 +12704,24 @@
         <v>84</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12744,16 +12747,16 @@
         <v>168</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -12802,7 +12805,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -12817,21 +12820,21 @@
         <v>81</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>21</v>
@@ -12853,19 +12856,19 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -12894,7 +12897,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
@@ -12912,7 +12915,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12927,18 +12930,18 @@
         <v>81</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13041,10 +13044,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13149,10 +13152,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13175,19 +13178,19 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -13236,7 +13239,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -13251,18 +13254,18 @@
         <v>81</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13288,20 +13291,20 @@
         <v>168</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q103" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R103" t="s" s="2">
         <v>21</v>
@@ -13325,10 +13328,10 @@
         <v>122</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -13346,7 +13349,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13361,18 +13364,18 @@
         <v>81</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13398,14 +13401,14 @@
         <v>85</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -13454,7 +13457,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -13469,18 +13472,18 @@
         <v>81</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13506,14 +13509,14 @@
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
@@ -13562,7 +13565,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -13571,24 +13574,24 @@
         <v>84</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13614,16 +13617,16 @@
         <v>168</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>21</v>
@@ -13672,7 +13675,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -13687,18 +13690,18 @@
         <v>81</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13721,19 +13724,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -13770,17 +13773,17 @@
         <v>21</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -13795,21 +13798,21 @@
         <v>81</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>21</v>
@@ -13831,19 +13834,19 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
@@ -13892,7 +13895,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -13907,18 +13910,18 @@
         <v>81</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14021,10 +14024,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14129,10 +14132,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14155,19 +14158,19 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>21</v>
@@ -14216,7 +14219,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14231,18 +14234,18 @@
         <v>81</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14268,20 +14271,20 @@
         <v>168</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q112" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R112" t="s" s="2">
         <v>21</v>
@@ -14305,10 +14308,10 @@
         <v>122</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>21</v>
@@ -14326,7 +14329,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14341,18 +14344,18 @@
         <v>81</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14378,14 +14381,14 @@
         <v>85</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -14434,7 +14437,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -14449,18 +14452,18 @@
         <v>81</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14486,14 +14489,14 @@
         <v>110</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>21</v>
@@ -14542,7 +14545,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -14551,24 +14554,24 @@
         <v>84</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14594,16 +14597,16 @@
         <v>168</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -14652,7 +14655,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14667,21 +14670,21 @@
         <v>81</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>21</v>
@@ -14703,19 +14706,19 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -14764,7 +14767,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -14779,18 +14782,18 @@
         <v>81</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14893,10 +14896,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15001,10 +15004,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15027,16 +15030,16 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15086,7 +15089,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -15098,21 +15101,21 @@
         <v>21</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15215,10 +15218,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15323,10 +15326,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15349,19 +15352,19 @@
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>21</v>
@@ -15410,7 +15413,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -15425,18 +15428,18 @@
         <v>81</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15462,20 +15465,20 @@
         <v>168</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q123" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R123" t="s" s="2">
         <v>21</v>
@@ -15499,10 +15502,10 @@
         <v>122</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>21</v>
@@ -15520,7 +15523,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -15535,18 +15538,18 @@
         <v>81</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15572,14 +15575,14 @@
         <v>85</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>21</v>
@@ -15628,7 +15631,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -15643,18 +15646,18 @@
         <v>81</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15680,14 +15683,14 @@
         <v>110</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>21</v>
@@ -15736,7 +15739,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15745,24 +15748,24 @@
         <v>84</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15788,16 +15791,16 @@
         <v>168</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>21</v>
@@ -15846,7 +15849,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -15861,18 +15864,18 @@
         <v>81</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15895,16 +15898,16 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -15954,7 +15957,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -15966,21 +15969,21 @@
         <v>21</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16083,10 +16086,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16191,10 +16194,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16217,19 +16220,19 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>21</v>
@@ -16278,7 +16281,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -16293,18 +16296,18 @@
         <v>81</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16330,20 +16333,20 @@
         <v>168</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q131" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R131" t="s" s="2">
         <v>21</v>
@@ -16367,10 +16370,10 @@
         <v>122</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>21</v>
@@ -16388,7 +16391,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -16403,18 +16406,18 @@
         <v>81</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16440,14 +16443,14 @@
         <v>85</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>21</v>
@@ -16496,7 +16499,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -16511,18 +16514,18 @@
         <v>81</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16548,14 +16551,14 @@
         <v>110</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>21</v>
@@ -16604,7 +16607,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -16613,24 +16616,24 @@
         <v>84</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16656,16 +16659,16 @@
         <v>168</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>21</v>
@@ -16714,7 +16717,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -16729,21 +16732,21 @@
         <v>81</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>21</v>
@@ -16765,19 +16768,19 @@
         <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>21</v>
@@ -16826,7 +16829,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -16841,18 +16844,18 @@
         <v>81</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16955,10 +16958,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17063,10 +17066,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17089,13 +17092,13 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -17146,7 +17149,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -17161,7 +17164,7 @@
         <v>81</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>21</v>
@@ -17169,10 +17172,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17275,10 +17278,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17383,10 +17386,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17409,19 +17412,19 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>21</v>
@@ -17470,7 +17473,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -17485,18 +17488,18 @@
         <v>81</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17522,20 +17525,20 @@
         <v>168</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>196</v>
+        <v>372</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q142" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R142" t="s" s="2">
         <v>21</v>
@@ -17559,10 +17562,10 @@
         <v>122</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>21</v>
@@ -17580,7 +17583,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -17595,18 +17598,18 @@
         <v>81</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17632,14 +17635,14 @@
         <v>85</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>21</v>
@@ -17688,7 +17691,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -17703,18 +17706,18 @@
         <v>81</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17740,14 +17743,14 @@
         <v>110</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>21</v>
@@ -17796,7 +17799,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -17805,24 +17808,24 @@
         <v>84</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17848,16 +17851,16 @@
         <v>168</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>21</v>
@@ -17906,7 +17909,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
@@ -17921,18 +17924,18 @@
         <v>81</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17955,13 +17958,13 @@
         <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -18012,7 +18015,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -18027,7 +18030,7 @@
         <v>81</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>21</v>
@@ -18035,10 +18038,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18141,10 +18144,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18249,10 +18252,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18275,19 +18278,19 @@
         <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>21</v>
@@ -18336,7 +18339,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>76</v>
@@ -18351,18 +18354,18 @@
         <v>81</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18388,20 +18391,20 @@
         <v>168</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>196</v>
+        <v>372</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q150" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R150" t="s" s="2">
         <v>21</v>
@@ -18425,10 +18428,10 @@
         <v>122</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>21</v>
@@ -18446,7 +18449,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -18461,18 +18464,18 @@
         <v>81</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18498,14 +18501,14 @@
         <v>85</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>21</v>
@@ -18554,7 +18557,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -18569,18 +18572,18 @@
         <v>81</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18606,14 +18609,14 @@
         <v>110</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>21</v>
@@ -18662,7 +18665,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>76</v>
@@ -18671,24 +18674,24 @@
         <v>84</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18714,16 +18717,16 @@
         <v>168</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>21</v>
@@ -18772,7 +18775,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
@@ -18787,18 +18790,18 @@
         <v>81</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18821,19 +18824,19 @@
         <v>91</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>21</v>
@@ -18882,7 +18885,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -18897,18 +18900,18 @@
         <v>81</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19011,10 +19014,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19119,10 +19122,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19145,13 +19148,13 @@
         <v>91</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -19202,7 +19205,7 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -19217,7 +19220,7 @@
         <v>81</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>21</v>
@@ -19225,10 +19228,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19331,10 +19334,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19439,10 +19442,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19465,19 +19468,19 @@
         <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>21</v>
@@ -19526,7 +19529,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -19541,18 +19544,18 @@
         <v>81</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19578,20 +19581,20 @@
         <v>168</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>196</v>
+        <v>372</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q161" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R161" t="s" s="2">
         <v>21</v>
@@ -19615,10 +19618,10 @@
         <v>122</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>21</v>
@@ -19636,7 +19639,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -19651,18 +19654,18 @@
         <v>81</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19688,14 +19691,14 @@
         <v>85</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>21</v>
@@ -19744,7 +19747,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -19759,18 +19762,18 @@
         <v>81</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19796,14 +19799,14 @@
         <v>110</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
@@ -19852,7 +19855,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
@@ -19861,24 +19864,24 @@
         <v>84</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19904,16 +19907,16 @@
         <v>168</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>21</v>
@@ -19962,7 +19965,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -19977,18 +19980,18 @@
         <v>81</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20011,13 +20014,13 @@
         <v>91</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -20068,7 +20071,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -20083,7 +20086,7 @@
         <v>81</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>21</v>
@@ -20091,10 +20094,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20197,10 +20200,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20305,10 +20308,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -20331,19 +20334,19 @@
         <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>21</v>
@@ -20392,7 +20395,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -20407,18 +20410,18 @@
         <v>81</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20444,20 +20447,20 @@
         <v>168</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>196</v>
+        <v>372</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q169" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R169" t="s" s="2">
         <v>21</v>
@@ -20481,10 +20484,10 @@
         <v>122</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>21</v>
@@ -20502,7 +20505,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -20517,18 +20520,18 @@
         <v>81</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20554,14 +20557,14 @@
         <v>85</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>21</v>
@@ -20610,7 +20613,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -20625,18 +20628,18 @@
         <v>81</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20662,14 +20665,14 @@
         <v>110</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -20718,7 +20721,7 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>76</v>
@@ -20727,24 +20730,24 @@
         <v>84</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20770,16 +20773,16 @@
         <v>168</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>21</v>
@@ -20828,7 +20831,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>76</v>
@@ -20843,18 +20846,18 @@
         <v>81</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20877,19 +20880,19 @@
         <v>91</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
@@ -20938,7 +20941,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -20950,10 +20953,10 @@
         <v>21</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>21</v>
@@ -20961,10 +20964,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21067,10 +21070,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -21175,10 +21178,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21201,19 +21204,19 @@
         <v>91</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>21</v>
@@ -21262,7 +21265,7 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -21277,18 +21280,18 @@
         <v>81</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21314,20 +21317,20 @@
         <v>168</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q177" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R177" t="s" s="2">
         <v>21</v>
@@ -21351,10 +21354,10 @@
         <v>122</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>21</v>
@@ -21372,7 +21375,7 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
@@ -21387,18 +21390,18 @@
         <v>81</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -21424,14 +21427,14 @@
         <v>85</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>21</v>
@@ -21480,7 +21483,7 @@
         <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>76</v>
@@ -21495,18 +21498,18 @@
         <v>81</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21532,14 +21535,14 @@
         <v>110</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>21</v>
@@ -21588,7 +21591,7 @@
         <v>21</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -21597,24 +21600,24 @@
         <v>84</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -21640,16 +21643,16 @@
         <v>168</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>21</v>
@@ -21698,7 +21701,7 @@
         <v>21</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -21713,18 +21716,18 @@
         <v>81</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21747,17 +21750,17 @@
         <v>91</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>21</v>
@@ -21806,7 +21809,7 @@
         <v>21</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -21818,10 +21821,10 @@
         <v>21</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>21</v>
@@ -21829,10 +21832,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -21935,10 +21938,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -22043,10 +22046,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22069,19 +22072,19 @@
         <v>91</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>21</v>
@@ -22130,7 +22133,7 @@
         <v>21</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -22145,18 +22148,18 @@
         <v>81</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -22182,20 +22185,20 @@
         <v>168</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q185" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R185" t="s" s="2">
         <v>21</v>
@@ -22219,10 +22222,10 @@
         <v>122</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>21</v>
@@ -22240,7 +22243,7 @@
         <v>21</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -22255,18 +22258,18 @@
         <v>81</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -22292,14 +22295,14 @@
         <v>85</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>21</v>
@@ -22348,7 +22351,7 @@
         <v>21</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>
@@ -22363,18 +22366,18 @@
         <v>81</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -22400,14 +22403,14 @@
         <v>110</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>21</v>
@@ -22456,7 +22459,7 @@
         <v>21</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>76</v>
@@ -22465,24 +22468,24 @@
         <v>84</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -22508,16 +22511,16 @@
         <v>168</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>21</v>
@@ -22566,7 +22569,7 @@
         <v>21</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>76</v>
@@ -22581,10 +22584,10 @@
         <v>81</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-freetext-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
